--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137263750</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>137263964</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137263750</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>137263964</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137263750</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>137263964</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39997-2026 artfynd.xlsx
+++ b/artfynd/A 39997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137264018</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137264061</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137264109</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137264149</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137264181</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137264210</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137264134</v>
       </c>
       <c r="B8" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137263750</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>137263964</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
